--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_219_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_219_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M2" t="n">
         <v>9</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,16 +1531,16 @@
         <v>25</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
         <v>3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>8</v>
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>3</v>
@@ -2511,16 +2511,16 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>4</v>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
         <v>3</v>
@@ -3099,7 +3099,7 @@
         <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>14</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>5</v>
@@ -3827,16 +3827,16 @@
         <v>59</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="X30" t="n">
         <v>26</v>
@@ -4684,7 +4684,7 @@
         <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         <v>32</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>10</v>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X41" t="n">
         <v>5</v>
@@ -5667,13 +5667,13 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -5863,13 +5863,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X43" t="n">
         <v>5</v>
@@ -6056,16 +6056,16 @@
         <v>22</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>6</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>149</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X48" t="n">
         <v>27</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_219_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_219_EL.xlsx
@@ -674,10 +674,10 @@
         <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -692,20 +692,20 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -854,17 +854,17 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
         <v>14</v>
       </c>
       <c r="W3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,10 +1543,10 @@
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,10 +2719,10 @@
         <v>3</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2752,25 +2752,25 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -3307,14 +3307,14 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>9</v>
       </c>
       <c r="X30" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -5088,14 +5088,14 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5124,22 +5124,22 @@
         <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
           <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -5480,10 +5480,10 @@
         <v>3</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>3</v>
       </c>
       <c r="X43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6796,14 +6796,14 @@
         <v>10</v>
       </c>
       <c r="X48" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Y48" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,22 +6832,22 @@
         <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
         <v>14</v>
       </c>
       <c r="AK48" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
